--- a/files/港岛-北角-海璇 II (第2B-3期).xlsx
+++ b/files/港岛-北角-海璇 II (第2B-3期).xlsx
@@ -8,9 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座 销控表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -113,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -178,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -11871,2536 +11733,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>海璇 II (第2B-3期) - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>26 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>25 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 2118呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 2115呎 (开放式)
-$13,680万
-$64,681/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 1438呎 (4+房)
-$7,026万
-$48,860/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 1117呎 (3房)
-$5,013万
-$44,879/呎
-(25年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 1438呎 (4+房)
-$6,411万
-$44,582/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 1117呎 (3房)
-$4,680万
-$41,898/呎
-(25年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 1438呎 (4+房)
-$6,277万
-$43,653/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 1117呎 (3房)
-$4,642万
-$41,558/呎
-(25年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 1438呎 (4+房)
-$6,129万
-$42,622/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 1117呎 (3房)
-$4,598万
-$41,162/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 1438呎 (4+房)
-$6,731万
-$46,809/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 1117呎 (3房)
-$4,538万
-$40,627/呎
-(24年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 1438呎 (4+房)
-$6,637万
-$46,156/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 1117呎 (3房)
-$4,397万
-$39,363/呎
-(24年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 1438呎 (4+房)
-$6,159万
-$42,828/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 1117呎 (3房)
-$4,436万
-$39,715/呎
-(25年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 1438呎 (4+房)
-$5,610万
-$39,009/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 1117呎 (3房)
-$4,537万
-$40,618/呎
-(24年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 1438呎 (4+房)
-$5,438万
-$37,816/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 1117呎 (3房)
-$4,220万
-$37,780/呎
-(25年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 1438呎 (4+房)
-$5,600万
-$38,943/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 1117呎 (3房)
-$3,960万
-$35,452/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 1438呎 (4+房)
-$5,268万
-$36,636/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 1117呎 (3房)
-$4,016万
-$35,952/呎
-(25年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 1372呎 (4+房)
-$6,806万
-$49,609/呎
-(25年-04月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 1063呎 (3房)
-$4,218万
-$39,680/呎
-(24年-12月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>海璇 II (第2B-3期) - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>28 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>27 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>A | 2108呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 2058呎 (4+房)
-$12,863万
-$62,504/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 1437呎 (4+房)
-$6,379万
-$44,388/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 1107呎 (3房)
-$4,850万
-$43,812/呎
-(25年-01月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 1437呎 (4+房)
-$5,902万
-$41,074/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 1107呎 (3房)
-$4,727万
-$42,704/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 1437呎 (4+房)
-$6,008万
-$41,809/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 1107呎 (3房)
-$4,645万
-$41,964/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 1437呎 (4+房)
-$5,739万
-$39,936/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 1107呎 (3房)
-$4,450万
-$40,199/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 1437呎 (4+房)
-$5,450万
-$37,926/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 1107呎 (3房)
-$5,001万
-$45,172/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 1437呎 (4+房)
-$5,887万
-$40,967/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 1107呎 (3房)
-$4,280万
-$38,663/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 1437呎 (4+房)
-$5,454万
-$37,957/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 1107呎 (3房)
-$4,119万
-$37,207/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 1437呎 (4+房)
-$5,420万
-$37,717/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 1107呎 (3房)
-$4,214万
-$38,067/呎
-(24年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 1437呎 (4+房)
-$5,372万
-$37,385/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 1107呎 (3房)
-$4,100万
-$37,037/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 1437呎 (4+房)
-$5,468万
-$38,051/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 1107呎 (3房)
-$4,087万
-$36,918/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 1437呎 (4+房)
-$4,968万
-$34,572/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 1107呎 (3房)
-$3,920万
-$35,411/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 1437呎 (4+房)
-$5,116万
-$35,604/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 1153呎 (3房)
-$3,984万
-$34,550/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 1437呎 (4+房)
-$5,478万
-$38,120/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 1090呎 (3房)
-$4,289万
-$39,348/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>海璇 II (第2B-3期) - 5座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>174 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>173 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 959呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 364呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 386呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 387呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
-        <is>
-          <t>G | 304呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>H | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>J | 365呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K6" s="16" t="inlineStr">
-        <is>
-          <t>K | 377呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L6" s="16" t="inlineStr">
-        <is>
-          <t>L | 373呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 1053呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 364呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>E | 387呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>F | 387呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>G | 304呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>H | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>J | 365呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K7" s="16" t="inlineStr">
-        <is>
-          <t>K | 377呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L7" s="16" t="inlineStr">
-        <is>
-          <t>L | 373呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 670呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 512呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>C | 364呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 387呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 387呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
-        <is>
-          <t>G | 304呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>H | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>J | 365呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K8" s="16" t="inlineStr">
-        <is>
-          <t>K | 377呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L8" s="16" t="inlineStr">
-        <is>
-          <t>L | 373呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 670呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 512呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>C | 364呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 353呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 387呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 387呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
-        <is>
-          <t>G | 304呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>H | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>J | 365呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K9" s="16" t="inlineStr">
-        <is>
-          <t>K | 377呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L9" s="16" t="inlineStr">
-        <is>
-          <t>L | 373呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 670呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 512呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 364呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 387呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>F | 387呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
-        <is>
-          <t>G | 304呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>H | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>J | 365呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K10" s="16" t="inlineStr">
-        <is>
-          <t>K | 377呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L10" s="16" t="inlineStr">
-        <is>
-          <t>L | 373呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 670呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 509呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 364呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 387呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>F | 387呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>G | 304呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>H | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>J | 365呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K11" s="16" t="inlineStr">
-        <is>
-          <t>K | 377呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L11" s="16" t="inlineStr">
-        <is>
-          <t>L | 373呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 670呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 509呎 (2房)
-$6,827万
-$134,126/呎
-(25年-05月)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>C | 364呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 387呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>F | 387呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>G | 304呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>H | 358呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>J | 365呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K12" s="16" t="inlineStr">
-        <is>
-          <t>K | 377呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L12" s="16" t="inlineStr">
-        <is>
-          <t>L | 373呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A | 671呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>B | 509呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>C | 364呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 353呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 387呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>F | 386呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>G | 304呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>H | 358呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>J | 365呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K13" s="16" t="inlineStr">
-        <is>
-          <t>K | 377呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L13" s="16" t="inlineStr">
-        <is>
-          <t>L | 373呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 670呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 509呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>C | 364呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 353呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 386呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>F | 387呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>G | 304呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>H | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>J | 365呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K14" s="16" t="inlineStr">
-        <is>
-          <t>K | 377呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L14" s="16" t="inlineStr">
-        <is>
-          <t>L | 373呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 671呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 509呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 364呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 387呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>F | 386呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>G | 304呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>H | 358呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>J | 365呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K15" s="16" t="inlineStr">
-        <is>
-          <t>K | 377呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>L | 372呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A | 671呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>B | 509呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>C | 364呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 387呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>F | 386呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>G | 304呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>H | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>J | 365呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K16" s="16" t="inlineStr">
-        <is>
-          <t>K | 377呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L16" s="16" t="inlineStr">
-        <is>
-          <t>L | 373呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A | 671呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>B | 509呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 364呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 353呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 386呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>F | 386呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>G | 304呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>H | 358呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>J | 365呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K17" s="16" t="inlineStr">
-        <is>
-          <t>K | 377呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L17" s="16" t="inlineStr">
-        <is>
-          <t>L | 373呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 671呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 509呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 364呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 387呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 387呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>G | 304呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>H | 361呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>J | 365呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K18" s="16" t="inlineStr">
-        <is>
-          <t>K | 377呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L18" s="16" t="inlineStr">
-        <is>
-          <t>L | 373呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 670呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 509呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 364呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 387呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 386呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>G | 304呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>H | 358呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>J | 365呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K19" s="16" t="inlineStr">
-        <is>
-          <t>K | 377呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L19" s="16" t="inlineStr">
-        <is>
-          <t>L | 373呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 671呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 509呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 364呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 356呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 387呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 387呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>G | 304呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>H | 358呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>J | 365呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K20" s="16" t="inlineStr">
-        <is>
-          <t>K | 377呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L20" s="16" t="inlineStr">
-        <is>
-          <t>L | 373呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 670呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 509呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 364呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 334呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 349呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 371呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>G | 304呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>H | 358呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>J | 365呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="K21" s="16" t="inlineStr">
-        <is>
-          <t>K | 355呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="L21" s="16" t="inlineStr">
-        <is>
-          <t>L | 351呎 (1房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-北角-海璇 II (第2B-3期).xlsx
+++ b/files/港岛-北角-海璇 II (第2B-3期).xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +44,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +144,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +225,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +655,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -11733,4 +11914,2536 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 2118呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 2115呎 (开放式)
+$13680万
+$64,681/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 1438呎 (4+房)
+$7026万
+$48,860/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1117呎 (3房)
+$5013万
+$44,879/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 1438呎 (4+房)
+$6411万
+$44,582/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 1117呎 (3房)
+$4680万
+$41,898/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1438呎 (4+房)
+$6277万
+$43,653/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 1117呎 (3房)
+$4642万
+$41,558/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1438呎 (4+房)
+$6129万
+$42,622/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1117呎 (3房)
+$4598万
+$41,162/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1438呎 (4+房)
+$6731万
+$46,809/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1117呎 (3房)
+$4538万
+$40,627/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1438呎 (4+房)
+$6637万
+$46,156/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1117呎 (3房)
+$4397万
+$39,363/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1438呎 (4+房)
+$6159万
+$42,828/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1117呎 (3房)
+$4436万
+$39,715/呎
+(25年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1438呎 (4+房)
+$5610万
+$39,009/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1117呎 (3房)
+$4537万
+$40,618/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 1438呎 (4+房)
+$5438万
+$37,816/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1117呎 (3房)
+$4220万
+$37,780/呎
+(25年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1438呎 (4+房)
+$5600万
+$38,943/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1117呎 (3房)
+$3960万
+$35,452/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 1438呎 (4+房)
+$5268万
+$36,636/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 1117呎 (3房)
+$4016万
+$35,952/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1372呎 (4+房)
+$6806万
+$49,609/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 1063呎 (3房)
+$4218万
+$39,680/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>A | 2108呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 2058呎 (4+房)
+$12863万
+$62,504/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 1437呎 (4+房)
+$6379万
+$44,388/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 1107呎 (3房)
+$4850万
+$43,812/呎
+(25年-01月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 1437呎 (4+房)
+$5902万
+$41,074/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 1107呎 (3房)
+$4727万
+$42,704/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 1437呎 (4+房)
+$6008万
+$41,809/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 1107呎 (3房)
+$4645万
+$41,964/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 1437呎 (4+房)
+$5739万
+$39,936/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 1107呎 (3房)
+$4450万
+$40,199/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 1437呎 (4+房)
+$5450万
+$37,926/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1107呎 (3房)
+$5001万
+$45,172/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1437呎 (4+房)
+$5887万
+$40,967/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1107呎 (3房)
+$4280万
+$38,663/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 1437呎 (4+房)
+$5454万
+$37,957/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 1107呎 (3房)
+$4119万
+$37,207/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 1437呎 (4+房)
+$5420万
+$37,717/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 1107呎 (3房)
+$4214万
+$38,067/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 1437呎 (4+房)
+$5372万
+$37,385/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1107呎 (3房)
+$4100万
+$37,037/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1437呎 (4+房)
+$5468万
+$38,051/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1107呎 (3房)
+$4087万
+$36,918/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 1437呎 (4+房)
+$4968万
+$34,572/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 1107呎 (3房)
+$3920万
+$35,411/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 1437呎 (4+房)
+$5116万
+$35,604/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 1153呎 (3房)
+$3984万
+$34,550/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 1437呎 (4+房)
+$5478万
+$38,120/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 1090呎 (3房)
+$4289万
+$39,348/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 959呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 364呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 386呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 387呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>G | 304呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>H | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>J | 365呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K5" s="20" t="inlineStr">
+        <is>
+          <t>K | 377呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>L | 373呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 1053呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 364呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>E | 387呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>F | 387呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>G | 304呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>H | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>J | 365呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>K | 377呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>L | 373呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 670呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 512呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 364呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 387呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 387呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>G | 304呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>H | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>J | 365呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>K | 377呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>L | 373呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 670呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 512呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>C | 364呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 353呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 387呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 387呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 304呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>H | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>J | 365呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>K | 377呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>L | 373呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 670呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 512呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 364呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 387呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>F | 387呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>G | 304呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>H | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>J | 365呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
+          <t>K | 377呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>L | 373呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 670呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 364呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 387呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>F | 387呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>G | 304呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>H | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>J | 365呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>K | 377呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>L | 373呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 670呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+$6827万
+$134,126/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 364呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 387呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 387呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>G | 304呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>H | 358呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>J | 365呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>K | 377呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>L | 373呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 671呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 364呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 353呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 387呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 386呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>G | 304呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>H | 358呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>J | 365呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K12" s="20" t="inlineStr">
+        <is>
+          <t>K | 377呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>L | 373呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 670呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 364呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 353呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 386呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 387呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>G | 304呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>H | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>J | 365呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="inlineStr">
+        <is>
+          <t>K | 377呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>L | 373呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 671呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 364呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 387呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 386呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>G | 304呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>H | 358呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>J | 365呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="inlineStr">
+        <is>
+          <t>K | 377呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L14" s="20" t="inlineStr">
+        <is>
+          <t>L | 372呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 671呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 364呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 387呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 386呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>G | 304呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>H | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>J | 365呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K15" s="20" t="inlineStr">
+        <is>
+          <t>K | 377呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L15" s="20" t="inlineStr">
+        <is>
+          <t>L | 373呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 671呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 364呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 353呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 386呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 386呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>G | 304呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>H | 358呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 365呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K16" s="20" t="inlineStr">
+        <is>
+          <t>K | 377呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
+        <is>
+          <t>L | 373呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 671呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 364呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 387呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 387呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 304呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>H | 361呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>J | 365呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K17" s="20" t="inlineStr">
+        <is>
+          <t>K | 377呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
+        <is>
+          <t>L | 373呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 670呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 364呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 387呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 386呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 304呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>H | 358呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>J | 365呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K18" s="20" t="inlineStr">
+        <is>
+          <t>K | 377呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L18" s="20" t="inlineStr">
+        <is>
+          <t>L | 373呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 671呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 364呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 356呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 387呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 387呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 304呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>H | 358呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>J | 365呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="inlineStr">
+        <is>
+          <t>K | 377呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L19" s="20" t="inlineStr">
+        <is>
+          <t>L | 373呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 670呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 509呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 364呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 334呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 349呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 371呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 304呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>H | 358呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>J | 365呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>K | 355呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="L20" s="20" t="inlineStr">
+        <is>
+          <t>L | 351呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-北角-海璇 II (第2B-3期).xlsx
+++ b/files/港岛-北角-海璇 II (第2B-3期).xlsx
@@ -655,7 +655,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-北角-海璇 II (第2B-3期).xlsx
+++ b/files/港岛-北角-海璇 II (第2B-3期).xlsx
@@ -645,7 +645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J230"/>
+  <dimension ref="A1:N230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -658,6 +658,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -715,6 +719,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -765,6 +789,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -811,6 +855,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -857,6 +921,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -903,6 +987,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -949,6 +1053,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -995,6 +1119,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1041,6 +1185,26 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1087,6 +1251,26 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1133,6 +1317,26 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1179,6 +1383,26 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1225,6 +1449,26 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1271,6 +1515,26 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1317,6 +1581,26 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1363,6 +1647,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1409,6 +1713,26 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1455,6 +1779,26 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1501,6 +1845,26 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1547,6 +1911,26 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1593,6 +1977,26 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1639,6 +2043,26 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1685,6 +2109,26 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1731,6 +2175,26 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1777,6 +2241,26 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1823,6 +2307,26 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1869,6 +2373,26 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1915,6 +2439,26 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1965,6 +2509,26 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -2011,6 +2575,26 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2057,6 +2641,26 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2103,6 +2707,26 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2149,6 +2773,26 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2195,6 +2839,26 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2241,6 +2905,26 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2287,6 +2971,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2333,6 +3037,26 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2379,6 +3103,26 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2425,6 +3169,26 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2471,6 +3235,26 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2517,6 +3301,26 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2563,6 +3367,26 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2609,6 +3433,26 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2655,6 +3499,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2701,6 +3565,26 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2747,6 +3631,26 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2793,6 +3697,26 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2839,6 +3763,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2885,6 +3829,26 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2931,6 +3895,26 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2977,6 +3961,26 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3023,6 +4027,26 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3069,6 +4093,26 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3115,6 +4159,26 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3161,6 +4225,26 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3207,6 +4291,26 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3257,6 +4361,26 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3307,6 +4431,26 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3357,6 +4501,26 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3407,6 +4571,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3457,6 +4641,26 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3507,6 +4711,26 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3557,6 +4781,26 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3607,6 +4851,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3657,6 +4921,26 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3707,6 +4991,26 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3757,6 +5061,26 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3807,6 +5131,26 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3857,6 +5201,26 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3907,6 +5271,26 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3957,6 +5341,26 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4007,6 +5411,26 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4057,6 +5481,26 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4107,6 +5551,26 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4157,6 +5621,26 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4207,6 +5691,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4257,6 +5761,26 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4307,6 +5831,26 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4357,6 +5901,26 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4407,6 +5971,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4457,6 +6041,26 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4507,6 +6111,26 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4557,6 +6181,26 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4607,6 +6251,26 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4657,6 +6321,26 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4707,6 +6391,26 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4757,6 +6461,26 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4807,6 +6531,26 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4857,6 +6601,26 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4907,6 +6671,26 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4957,6 +6741,26 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5007,6 +6811,26 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5057,6 +6881,26 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5107,6 +6951,26 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5157,6 +7021,26 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5207,6 +7091,26 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5257,6 +7161,26 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5307,6 +7231,26 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5357,6 +7301,26 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5407,6 +7371,26 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5457,6 +7441,26 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5507,6 +7511,26 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5557,6 +7581,26 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5607,6 +7651,26 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5657,6 +7721,26 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5707,6 +7791,26 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5757,6 +7861,26 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5807,6 +7931,26 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5857,6 +8001,26 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5907,6 +8071,26 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5957,6 +8141,26 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6007,6 +8211,26 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6057,6 +8281,26 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6107,6 +8351,26 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L114" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6157,6 +8421,26 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L115" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6207,6 +8491,26 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L116" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6257,6 +8561,26 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L117" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6307,6 +8631,26 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L118" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6357,6 +8701,26 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6407,6 +8771,26 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6457,6 +8841,26 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6507,6 +8911,26 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6557,6 +8981,26 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6607,6 +9051,26 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6657,6 +9121,26 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L125" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6707,6 +9191,26 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6757,6 +9261,26 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L127" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6807,6 +9331,26 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6857,6 +9401,26 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L129" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6903,6 +9467,26 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6953,6 +9537,26 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7003,6 +9607,26 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L132" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7053,6 +9677,26 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L133" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7103,6 +9747,26 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L134" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7153,6 +9817,26 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L135" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7203,6 +9887,26 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7253,6 +9957,26 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L137" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7303,6 +10027,26 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7353,6 +10097,26 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7403,6 +10167,26 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L140" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7453,6 +10237,26 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L141" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7503,6 +10307,26 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7553,6 +10377,26 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L143" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7603,6 +10447,26 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L144" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7653,6 +10517,26 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L145" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7703,6 +10587,26 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L146" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7753,6 +10657,26 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L147" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7803,6 +10727,26 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L148" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7853,6 +10797,26 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L149" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7903,6 +10867,26 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L150" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7953,6 +10937,26 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L151" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8003,6 +11007,26 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L152" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8053,6 +11077,26 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L153" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8103,6 +11147,26 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L154" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8153,6 +11217,26 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L155" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8203,6 +11287,26 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L156" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8253,6 +11357,26 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L157" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8303,6 +11427,26 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L158" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8353,6 +11497,26 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L159" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8403,6 +11567,26 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L160" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8453,6 +11637,26 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L161" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8503,6 +11707,26 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L162" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8553,6 +11777,26 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L163" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8603,6 +11847,26 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L164" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8653,6 +11917,26 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L165" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8703,6 +11987,26 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L166" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8753,6 +12057,26 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L167" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8803,6 +12127,26 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L168" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8853,6 +12197,26 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L169" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8903,6 +12267,26 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L170" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8953,6 +12337,26 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L171" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9003,6 +12407,26 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L172" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9053,6 +12477,26 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L173" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9103,6 +12547,26 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L174" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9153,6 +12617,26 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L175" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9203,6 +12687,26 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L176" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9253,6 +12757,26 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L177" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9303,6 +12827,26 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L178" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M178" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N178" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9353,6 +12897,26 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L179" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9403,6 +12967,26 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L180" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N180" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9453,6 +13037,26 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L181" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9503,6 +13107,26 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L182" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N182" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9553,6 +13177,26 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L183" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9603,6 +13247,26 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L184" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9653,6 +13317,26 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L185" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9703,6 +13387,26 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K186" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L186" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9753,6 +13457,26 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K187" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L187" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N187" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9803,6 +13527,26 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K188" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L188" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9853,6 +13597,26 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K189" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L189" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N189" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9903,6 +13667,26 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K190" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L190" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N190" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9953,6 +13737,26 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K191" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L191" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N191" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10003,6 +13807,26 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K192" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L192" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N192" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10053,6 +13877,26 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L193" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M193" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N193" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10103,6 +13947,26 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K194" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L194" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M194" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N194" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10153,6 +14017,26 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K195" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L195" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M195" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N195" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10203,6 +14087,26 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K196" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L196" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M196" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N196" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10253,6 +14157,26 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K197" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L197" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M197" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N197" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10303,6 +14227,26 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K198" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L198" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M198" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N198" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10353,6 +14297,26 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K199" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L199" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M199" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N199" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10403,6 +14367,26 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K200" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L200" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M200" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N200" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10453,6 +14437,26 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K201" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L201" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N201" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10503,6 +14507,26 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K202" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L202" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M202" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N202" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10553,6 +14577,26 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K203" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L203" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M203" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N203" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10603,6 +14647,26 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L204" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N204" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10653,6 +14717,26 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L205" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N205" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10703,6 +14787,26 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L206" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M206" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N206" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10753,6 +14857,26 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L207" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M207" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N207" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10803,6 +14927,26 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L208" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M208" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N208" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10853,6 +14997,26 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L209" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M209" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N209" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10903,6 +15067,26 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L210" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M210" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N210" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10953,6 +15137,26 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L211" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M211" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N211" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11003,6 +15207,26 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L212" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M212" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N212" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11053,6 +15277,26 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L213" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M213" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N213" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11103,6 +15347,26 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L214" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M214" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N214" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11153,6 +15417,26 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L215" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M215" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N215" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11203,6 +15487,26 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K216" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L216" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M216" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N216" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11253,6 +15557,26 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L217" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M217" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N217" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11303,6 +15627,26 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L218" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M218" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N218" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11353,6 +15697,26 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L219" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N219" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11403,6 +15767,26 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L220" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M220" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N220" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11453,6 +15837,26 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L221" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M221" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N221" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11503,6 +15907,26 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L222" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M222" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N222" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11553,6 +15977,26 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L223" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M223" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N223" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11603,6 +16047,26 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L224" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M224" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N224" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11653,6 +16117,26 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L225" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M225" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N225" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11703,6 +16187,26 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L226" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M226" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11753,6 +16257,26 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L227" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M227" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N227" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11803,6 +16327,26 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K228" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L228" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M228" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N228" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11853,6 +16397,26 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L229" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M229" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11903,13 +16467,33 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L230" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M230" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -12045,7 +16629,7 @@
           <t>A | 2115呎 (开放式)
 $13680万
 $64,681/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -12061,7 +16645,7 @@
           <t>A | 1438呎 (4+房)
 $7026万
 $48,860/呎
-(25年-04月)</t>
+(25年-04月-22日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -12069,7 +16653,7 @@
           <t>B | 1117呎 (3房)
 $5013万
 $44,879/呎
-(25年-04月)</t>
+(25年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -12084,7 +16668,7 @@
           <t>A | 1438呎 (4+房)
 $6411万
 $44,582/呎
-(25年-04月)</t>
+(25年-04月-22日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -12092,7 +16676,7 @@
           <t>B | 1117呎 (3房)
 $4680万
 $41,898/呎
-(25年-04月)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -12107,7 +16691,7 @@
           <t>A | 1438呎 (4+房)
 $6277万
 $43,653/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -12115,7 +16699,7 @@
           <t>B | 1117呎 (3房)
 $4642万
 $41,558/呎
-(25年-04月)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -12130,7 +16714,7 @@
           <t>A | 1438呎 (4+房)
 $6129万
 $42,622/呎
-(24年-12月)</t>
+(24年-12月-04日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -12138,7 +16722,7 @@
           <t>B | 1117呎 (3房)
 $4598万
 $41,162/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
     </row>
@@ -12153,7 +16737,7 @@
           <t>A | 1438呎 (4+房)
 $6731万
 $46,809/呎
-(24年-12月)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -12161,7 +16745,7 @@
           <t>B | 1117呎 (3房)
 $4538万
 $40,627/呎
-(24年-12月)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
     </row>
@@ -12176,7 +16760,7 @@
           <t>A | 1438呎 (4+房)
 $6637万
 $46,156/呎
-(24年-12月)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -12184,7 +16768,7 @@
           <t>B | 1117呎 (3房)
 $4397万
 $39,363/呎
-(24年-12月)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
     </row>
@@ -12199,7 +16783,7 @@
           <t>A | 1438呎 (4+房)
 $6159万
 $42,828/呎
-(25年-04月)</t>
+(25年-04月-21日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -12207,7 +16791,7 @@
           <t>B | 1117呎 (3房)
 $4436万
 $39,715/呎
-(25年-05月)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
     </row>
@@ -12222,7 +16806,7 @@
           <t>A | 1438呎 (4+房)
 $5610万
 $39,009/呎
-(24年-11月)</t>
+(24年-11月-20日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -12230,7 +16814,7 @@
           <t>B | 1117呎 (3房)
 $4537万
 $40,618/呎
-(24年-12月)</t>
+(24年-12月-29日)</t>
         </is>
       </c>
     </row>
@@ -12245,7 +16829,7 @@
           <t>A | 1438呎 (4+房)
 $5438万
 $37,816/呎
-(25年-04月)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -12253,7 +16837,7 @@
           <t>B | 1117呎 (3房)
 $4220万
 $37,780/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
     </row>
@@ -12268,7 +16852,7 @@
           <t>A | 1438呎 (4+房)
 $5600万
 $38,943/呎
-(24年-12月)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -12276,7 +16860,7 @@
           <t>B | 1117呎 (3房)
 $3960万
 $35,452/呎
-(25年-03月)</t>
+(25年-03月-02日)</t>
         </is>
       </c>
     </row>
@@ -12291,7 +16875,7 @@
           <t>A | 1438呎 (4+房)
 $5268万
 $36,636/呎
-(25年-05月)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -12299,7 +16883,7 @@
           <t>B | 1117呎 (3房)
 $4016万
 $35,952/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -12314,7 +16898,7 @@
           <t>A | 1372呎 (4+房)
 $6806万
 $49,609/呎
-(25年-04月)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -12322,7 +16906,7 @@
           <t>B | 1063呎 (3房)
 $4218万
 $39,680/呎
-(24年-12月)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
     </row>
@@ -12464,7 +17048,7 @@
           <t>A | 2058呎 (4+房)
 $12863万
 $62,504/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -12480,7 +17064,7 @@
           <t>A | 1437呎 (4+房)
 $6379万
 $44,388/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -12488,7 +17072,7 @@
           <t>B | 1107呎 (3房)
 $4850万
 $43,812/呎
-(25年-01月)</t>
+(25年-01月-12日)</t>
         </is>
       </c>
     </row>
@@ -12503,7 +17087,7 @@
           <t>A | 1437呎 (4+房)
 $5902万
 $41,074/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -12511,7 +17095,7 @@
           <t>B | 1107呎 (3房)
 $4727万
 $42,704/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
     </row>
@@ -12526,7 +17110,7 @@
           <t>A | 1437呎 (4+房)
 $6008万
 $41,809/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -12534,7 +17118,7 @@
           <t>B | 1107呎 (3房)
 $4645万
 $41,964/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
     </row>
@@ -12549,7 +17133,7 @@
           <t>A | 1437呎 (4+房)
 $5739万
 $39,936/呎
-(24年-10月)</t>
+(24年-10月-16日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -12557,7 +17141,7 @@
           <t>B | 1107呎 (3房)
 $4450万
 $40,199/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
     </row>
@@ -12572,7 +17156,7 @@
           <t>A | 1437呎 (4+房)
 $5450万
 $37,926/呎
-(24年-10月)</t>
+(24年-10月-17日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -12580,7 +17164,7 @@
           <t>B | 1107呎 (3房)
 $5001万
 $45,172/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
     </row>
@@ -12595,7 +17179,7 @@
           <t>A | 1437呎 (4+房)
 $5887万
 $40,967/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -12603,7 +17187,7 @@
           <t>B | 1107呎 (3房)
 $4280万
 $38,663/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
     </row>
@@ -12618,7 +17202,7 @@
           <t>A | 1437呎 (4+房)
 $5454万
 $37,957/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -12626,7 +17210,7 @@
           <t>B | 1107呎 (3房)
 $4119万
 $37,207/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
     </row>
@@ -12641,7 +17225,7 @@
           <t>A | 1437呎 (4+房)
 $5420万
 $37,717/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -12649,7 +17233,7 @@
           <t>B | 1107呎 (3房)
 $4214万
 $38,067/呎
-(24年-12月)</t>
+(24年-12月-01日)</t>
         </is>
       </c>
     </row>
@@ -12664,7 +17248,7 @@
           <t>A | 1437呎 (4+房)
 $5372万
 $37,385/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -12672,7 +17256,7 @@
           <t>B | 1107呎 (3房)
 $4100万
 $37,037/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
     </row>
@@ -12687,7 +17271,7 @@
           <t>A | 1437呎 (4+房)
 $5468万
 $38,051/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -12695,7 +17279,7 @@
           <t>B | 1107呎 (3房)
 $4087万
 $36,918/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
     </row>
@@ -12710,7 +17294,7 @@
           <t>A | 1437呎 (4+房)
 $4968万
 $34,572/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -12718,7 +17302,7 @@
           <t>B | 1107呎 (3房)
 $3920万
 $35,411/呎
-(24年-10月)</t>
+(24年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -12733,7 +17317,7 @@
           <t>A | 1437呎 (4+房)
 $5116万
 $35,604/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -12741,7 +17325,7 @@
           <t>B | 1153呎 (3房)
 $3984万
 $34,550/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
     </row>
@@ -12756,7 +17340,7 @@
           <t>A | 1437呎 (4+房)
 $5478万
 $38,120/呎
-(24年-11月)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -12764,7 +17348,7 @@
           <t>B | 1090呎 (3房)
 $4289万
 $39,348/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
     </row>
@@ -13508,7 +18092,7 @@
           <t>B | 509呎 (2房)
 $6827万
 $134,126/呎
-(25年-05月)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">

--- a/files/港岛-北角-海璇 II (第2B-3期).xlsx
+++ b/files/港岛-北角-海璇 II (第2B-3期).xlsx
@@ -3611,7 +3611,7 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>1437</v>
+        <v>1483</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>54200000</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>37717</v>
+        <v>36548</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="E77" s="4" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
           <t>A | 2115呎 (开放式)
 $13680万
 $64,681/呎
-(25年-11月-10日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -16645,7 +16645,7 @@
           <t>A | 1438呎 (4+房)
 $7026万
 $48,860/呎
-(25年-04月-22日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -16653,7 +16653,7 @@
           <t>B | 1117呎 (3房)
 $5013万
 $44,879/呎
-(25年-04月-22日)</t>
+(25年-04月)</t>
         </is>
       </c>
     </row>
@@ -16668,7 +16668,7 @@
           <t>A | 1438呎 (4+房)
 $6411万
 $44,582/呎
-(25年-04月-22日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -16676,7 +16676,7 @@
           <t>B | 1117呎 (3房)
 $4680万
 $41,898/呎
-(25年-04月-02日)</t>
+(25年-04月)</t>
         </is>
       </c>
     </row>
@@ -16691,7 +16691,7 @@
           <t>A | 1438呎 (4+房)
 $6277万
 $43,653/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -16699,7 +16699,7 @@
           <t>B | 1117呎 (3房)
 $4642万
 $41,558/呎
-(25年-04月-29日)</t>
+(25年-04月)</t>
         </is>
       </c>
     </row>
@@ -16714,7 +16714,7 @@
           <t>A | 1438呎 (4+房)
 $6129万
 $42,622/呎
-(24年-12月-04日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -16722,7 +16722,7 @@
           <t>B | 1117呎 (3房)
 $4598万
 $41,162/呎
-(25年-03月-18日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
           <t>A | 1438呎 (4+房)
 $6731万
 $46,809/呎
-(24年-12月-05日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -16745,7 +16745,7 @@
           <t>B | 1117呎 (3房)
 $4538万
 $40,627/呎
-(24年-12月-18日)</t>
+(24年-12月)</t>
         </is>
       </c>
     </row>
@@ -16760,7 +16760,7 @@
           <t>A | 1438呎 (4+房)
 $6637万
 $46,156/呎
-(24年-12月-18日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -16768,7 +16768,7 @@
           <t>B | 1117呎 (3房)
 $4397万
 $39,363/呎
-(24年-12月-19日)</t>
+(24年-12月)</t>
         </is>
       </c>
     </row>
@@ -16783,7 +16783,7 @@
           <t>A | 1438呎 (4+房)
 $6159万
 $42,828/呎
-(25年-04月-21日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -16791,7 +16791,7 @@
           <t>B | 1117呎 (3房)
 $4436万
 $39,715/呎
-(25年-05月-08日)</t>
+(25年-05月)</t>
         </is>
       </c>
     </row>
@@ -16806,7 +16806,7 @@
           <t>A | 1438呎 (4+房)
 $5610万
 $39,009/呎
-(24年-11月-20日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -16814,7 +16814,7 @@
           <t>B | 1117呎 (3房)
 $4537万
 $40,618/呎
-(24年-12月-29日)</t>
+(24年-12月)</t>
         </is>
       </c>
     </row>
@@ -16829,7 +16829,7 @@
           <t>A | 1438呎 (4+房)
 $5438万
 $37,816/呎
-(25年-04月-09日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -16837,7 +16837,7 @@
           <t>B | 1117呎 (3房)
 $4220万
 $37,780/呎
-(25年-04月-08日)</t>
+(25年-04月)</t>
         </is>
       </c>
     </row>
@@ -16852,7 +16852,7 @@
           <t>A | 1438呎 (4+房)
 $5600万
 $38,943/呎
-(24年-12月-10日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -16860,7 +16860,7 @@
           <t>B | 1117呎 (3房)
 $3960万
 $35,452/呎
-(25年-03月-02日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -16875,7 +16875,7 @@
           <t>A | 1438呎 (4+房)
 $5268万
 $36,636/呎
-(25年-05月-14日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -16883,7 +16883,7 @@
           <t>B | 1117呎 (3房)
 $4016万
 $35,952/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -16898,7 +16898,7 @@
           <t>A | 1372呎 (4+房)
 $6806万
 $49,609/呎
-(25年-04月-09日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -16906,7 +16906,7 @@
           <t>B | 1063呎 (3房)
 $4218万
 $39,680/呎
-(24年-12月-19日)</t>
+(24年-12月)</t>
         </is>
       </c>
     </row>
@@ -17048,7 +17048,7 @@
           <t>A | 2058呎 (4+房)
 $12863万
 $62,504/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -17064,7 +17064,7 @@
           <t>A | 1437呎 (4+房)
 $6379万
 $44,388/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -17072,7 +17072,7 @@
           <t>B | 1107呎 (3房)
 $4850万
 $43,812/呎
-(25年-01月-12日)</t>
+(25年-01月)</t>
         </is>
       </c>
     </row>
@@ -17087,7 +17087,7 @@
           <t>A | 1437呎 (4+房)
 $5902万
 $41,074/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -17095,7 +17095,7 @@
           <t>B | 1107呎 (3房)
 $4727万
 $42,704/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -17110,7 +17110,7 @@
           <t>A | 1437呎 (4+房)
 $6008万
 $41,809/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -17118,7 +17118,7 @@
           <t>B | 1107呎 (3房)
 $4645万
 $41,964/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -17133,7 +17133,7 @@
           <t>A | 1437呎 (4+房)
 $5739万
 $39,936/呎
-(24年-10月-16日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -17141,7 +17141,7 @@
           <t>B | 1107呎 (3房)
 $4450万
 $40,199/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -17156,7 +17156,7 @@
           <t>A | 1437呎 (4+房)
 $5450万
 $37,926/呎
-(24年-10月-17日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -17164,7 +17164,7 @@
           <t>B | 1107呎 (3房)
 $5001万
 $45,172/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -17179,7 +17179,7 @@
           <t>A | 1437呎 (4+房)
 $5887万
 $40,967/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -17187,7 +17187,7 @@
           <t>B | 1107呎 (3房)
 $4280万
 $38,663/呎
-(24年-10月-23日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -17202,7 +17202,7 @@
           <t>A | 1437呎 (4+房)
 $5454万
 $37,957/呎
-(24年-10月-23日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -17210,7 +17210,7 @@
           <t>B | 1107呎 (3房)
 $4119万
 $37,207/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -17222,10 +17222,10 @@
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>A | 1437呎 (4+房)
+          <t>A | 1483呎 (4+房)
 $5420万
-$37,717/呎
-(24年-11月-14日)</t>
+$36,548/呎
+(24年-11月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -17233,7 +17233,7 @@
           <t>B | 1107呎 (3房)
 $4214万
 $38,067/呎
-(24年-12月-01日)</t>
+(24年-12月)</t>
         </is>
       </c>
     </row>
@@ -17248,7 +17248,7 @@
           <t>A | 1437呎 (4+房)
 $5372万
 $37,385/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -17256,7 +17256,7 @@
           <t>B | 1107呎 (3房)
 $4100万
 $37,037/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -17271,7 +17271,7 @@
           <t>A | 1437呎 (4+房)
 $5468万
 $38,051/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -17279,7 +17279,7 @@
           <t>B | 1107呎 (3房)
 $4087万
 $36,918/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -17294,7 +17294,7 @@
           <t>A | 1437呎 (4+房)
 $4968万
 $34,572/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -17302,7 +17302,7 @@
           <t>B | 1107呎 (3房)
 $3920万
 $35,411/呎
-(24年-10月-20日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -17317,7 +17317,7 @@
           <t>A | 1437呎 (4+房)
 $5116万
 $35,604/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -17325,7 +17325,7 @@
           <t>B | 1153呎 (3房)
 $3984万
 $34,550/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -17340,7 +17340,7 @@
           <t>A | 1437呎 (4+房)
 $5478万
 $38,120/呎
-(24年-11月-27日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -17348,7 +17348,7 @@
           <t>B | 1090呎 (3房)
 $4289万
 $39,348/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -17781,7 +17781,7 @@
       </c>
       <c r="L7" s="20" t="inlineStr">
         <is>
-          <t>L | 373呎 (1房)
+          <t>L | 372呎 (1房)
 -
 -
 (待售)</t>
@@ -18092,7 +18092,7 @@
           <t>B | 509呎 (2房)
 $6827万
 $134,126/呎
-(25年-05月-19日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">

--- a/files/港岛-北角-海璇 II (第2B-3期).xlsx
+++ b/files/港岛-北角-海璇 II (第2B-3期).xlsx
@@ -16629,7 +16629,7 @@
           <t>A | 2115呎 (开放式)
 $13680万
 $64,681/呎
-(25年-11月)</t>
+(25年-11月-10日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -16645,7 +16645,7 @@
           <t>A | 1438呎 (4+房)
 $7026万
 $48,860/呎
-(25年-04月)</t>
+(25年-04月-22日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -16653,7 +16653,7 @@
           <t>B | 1117呎 (3房)
 $5013万
 $44,879/呎
-(25年-04月)</t>
+(25年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -16668,7 +16668,7 @@
           <t>A | 1438呎 (4+房)
 $6411万
 $44,582/呎
-(25年-04月)</t>
+(25年-04月-22日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -16676,7 +16676,7 @@
           <t>B | 1117呎 (3房)
 $4680万
 $41,898/呎
-(25年-04月)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -16691,7 +16691,7 @@
           <t>A | 1438呎 (4+房)
 $6277万
 $43,653/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -16699,7 +16699,7 @@
           <t>B | 1117呎 (3房)
 $4642万
 $41,558/呎
-(25年-04月)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
     </row>
@@ -16714,7 +16714,7 @@
           <t>A | 1438呎 (4+房)
 $6129万
 $42,622/呎
-(24年-12月)</t>
+(24年-12月-04日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -16722,7 +16722,7 @@
           <t>B | 1117呎 (3房)
 $4598万
 $41,162/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
           <t>A | 1438呎 (4+房)
 $6731万
 $46,809/呎
-(24年-12月)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -16745,7 +16745,7 @@
           <t>B | 1117呎 (3房)
 $4538万
 $40,627/呎
-(24年-12月)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
     </row>
@@ -16760,7 +16760,7 @@
           <t>A | 1438呎 (4+房)
 $6637万
 $46,156/呎
-(24年-12月)</t>
+(24年-12月-18日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -16768,7 +16768,7 @@
           <t>B | 1117呎 (3房)
 $4397万
 $39,363/呎
-(24年-12月)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
     </row>
@@ -16783,7 +16783,7 @@
           <t>A | 1438呎 (4+房)
 $6159万
 $42,828/呎
-(25年-04月)</t>
+(25年-04月-21日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -16791,7 +16791,7 @@
           <t>B | 1117呎 (3房)
 $4436万
 $39,715/呎
-(25年-05月)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
     </row>
@@ -16806,7 +16806,7 @@
           <t>A | 1438呎 (4+房)
 $5610万
 $39,009/呎
-(24年-11月)</t>
+(24年-11月-20日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -16814,7 +16814,7 @@
           <t>B | 1117呎 (3房)
 $4537万
 $40,618/呎
-(24年-12月)</t>
+(24年-12月-29日)</t>
         </is>
       </c>
     </row>
@@ -16829,7 +16829,7 @@
           <t>A | 1438呎 (4+房)
 $5438万
 $37,816/呎
-(25年-04月)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -16837,7 +16837,7 @@
           <t>B | 1117呎 (3房)
 $4220万
 $37,780/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
     </row>
@@ -16852,7 +16852,7 @@
           <t>A | 1438呎 (4+房)
 $5600万
 $38,943/呎
-(24年-12月)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -16860,7 +16860,7 @@
           <t>B | 1117呎 (3房)
 $3960万
 $35,452/呎
-(25年-03月)</t>
+(25年-03月-02日)</t>
         </is>
       </c>
     </row>
@@ -16875,7 +16875,7 @@
           <t>A | 1438呎 (4+房)
 $5268万
 $36,636/呎
-(25年-05月)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -16883,7 +16883,7 @@
           <t>B | 1117呎 (3房)
 $4016万
 $35,952/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -16898,7 +16898,7 @@
           <t>A | 1372呎 (4+房)
 $6806万
 $49,609/呎
-(25年-04月)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -16906,7 +16906,7 @@
           <t>B | 1063呎 (3房)
 $4218万
 $39,680/呎
-(24年-12月)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
     </row>
@@ -17048,7 +17048,7 @@
           <t>A | 2058呎 (4+房)
 $12863万
 $62,504/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -17064,7 +17064,7 @@
           <t>A | 1437呎 (4+房)
 $6379万
 $44,388/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -17072,7 +17072,7 @@
           <t>B | 1107呎 (3房)
 $4850万
 $43,812/呎
-(25年-01月)</t>
+(25年-01月-12日)</t>
         </is>
       </c>
     </row>
@@ -17087,7 +17087,7 @@
           <t>A | 1437呎 (4+房)
 $5902万
 $41,074/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -17095,7 +17095,7 @@
           <t>B | 1107呎 (3房)
 $4727万
 $42,704/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
     </row>
@@ -17110,7 +17110,7 @@
           <t>A | 1437呎 (4+房)
 $6008万
 $41,809/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -17118,7 +17118,7 @@
           <t>B | 1107呎 (3房)
 $4645万
 $41,964/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
     </row>
@@ -17133,7 +17133,7 @@
           <t>A | 1437呎 (4+房)
 $5739万
 $39,936/呎
-(24年-10月)</t>
+(24年-10月-16日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -17141,7 +17141,7 @@
           <t>B | 1107呎 (3房)
 $4450万
 $40,199/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
     </row>
@@ -17156,7 +17156,7 @@
           <t>A | 1437呎 (4+房)
 $5450万
 $37,926/呎
-(24年-10月)</t>
+(24年-10月-17日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -17164,7 +17164,7 @@
           <t>B | 1107呎 (3房)
 $5001万
 $45,172/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
     </row>
@@ -17179,7 +17179,7 @@
           <t>A | 1437呎 (4+房)
 $5887万
 $40,967/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -17187,7 +17187,7 @@
           <t>B | 1107呎 (3房)
 $4280万
 $38,663/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
     </row>
@@ -17202,7 +17202,7 @@
           <t>A | 1437呎 (4+房)
 $5454万
 $37,957/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -17210,7 +17210,7 @@
           <t>B | 1107呎 (3房)
 $4119万
 $37,207/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
           <t>A | 1483呎 (4+房)
 $5420万
 $36,548/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -17233,7 +17233,7 @@
           <t>B | 1107呎 (3房)
 $4214万
 $38,067/呎
-(24年-12月)</t>
+(24年-12月-01日)</t>
         </is>
       </c>
     </row>
@@ -17248,7 +17248,7 @@
           <t>A | 1437呎 (4+房)
 $5372万
 $37,385/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -17256,7 +17256,7 @@
           <t>B | 1107呎 (3房)
 $4100万
 $37,037/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
     </row>
@@ -17271,7 +17271,7 @@
           <t>A | 1437呎 (4+房)
 $5468万
 $38,051/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -17279,7 +17279,7 @@
           <t>B | 1107呎 (3房)
 $4087万
 $36,918/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
     </row>
@@ -17294,7 +17294,7 @@
           <t>A | 1437呎 (4+房)
 $4968万
 $34,572/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -17302,7 +17302,7 @@
           <t>B | 1107呎 (3房)
 $3920万
 $35,411/呎
-(24年-10月)</t>
+(24年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -17317,7 +17317,7 @@
           <t>A | 1437呎 (4+房)
 $5116万
 $35,604/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -17325,7 +17325,7 @@
           <t>B | 1153呎 (3房)
 $3984万
 $34,550/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
     </row>
@@ -17340,7 +17340,7 @@
           <t>A | 1437呎 (4+房)
 $5478万
 $38,120/呎
-(24年-11月)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -17348,7 +17348,7 @@
           <t>B | 1090呎 (3房)
 $4289万
 $39,348/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
     </row>
@@ -18092,7 +18092,7 @@
           <t>B | 509呎 (2房)
 $6827万
 $134,126/呎
-(25年-05月)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">

--- a/files/港岛-北角-海璇 II (第2B-3期).xlsx
+++ b/files/港岛-北角-海璇 II (第2B-3期).xlsx
@@ -15323,7 +15323,7 @@
         </is>
       </c>
       <c r="E214" s="4" t="n">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="G19" s="20" t="inlineStr">
         <is>
-          <t>F | 387呎 (1房)
+          <t>F | 386呎 (1房)
 -
 -
 (待售)</t>
